--- a/xlsx/換色紀錄表(2505) 6號盤存.xlsx
+++ b/xlsx/換色紀錄表(2505) 6號盤存.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d310cb6cf3413c87/換色紀錄表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="251" documentId="8_{F11015D4-0DB4-AE4D-835C-3BF05C3F4FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F4E0A02-D306-4593-AF2F-EC40F3E54445}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{C9EF893D-FFAD-2E4D-90DE-448718EA4348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11006,7 +11006,7 @@
       <c r="IV1" s="13"/>
       <c r="IW1" s="13"/>
     </row>
-    <row r="2" spans="1:257" s="22" customFormat="1" ht="33" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:257" s="22" customFormat="1" ht="24.75" x14ac:dyDescent="0.15">
       <c r="A2" s="124"/>
       <c r="B2" s="120" t="s">
         <v>321</v>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G2" s="21">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="H2" s="54" t="e">
         <f>TEXT(WEEKDAY(每日用粉紀錄表!#REF!,1),"aaaa")</f>
